--- a/assets/翻译/en-US.xlsx
+++ b/assets/翻译/en-US.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="846">
   <si>
     <t>key</t>
   </si>
@@ -580,6 +580,17 @@
   <si>
     <t>1v1 (You're the Host)
 &lt;size=10&gt;Other players can join your match. The match ends if you leave the scene.&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>YiDaYi_PvE</t>
+  </si>
+  <si>
+    <t>一打一（打电脑）
+&lt;size=12&gt;其他玩家可旁观您的战局，您退出场景就会结束战局&lt;/size&gt;</t>
+  </si>
+  <si>
+    <t>1v1 (vs AI)
+&lt;size=12&gt;Other players can spectate your battle. Exiting the scene will end the battle.&lt;/size&gt;</t>
   </si>
   <si>
     <t>DuoWanJiaHunZhan_ShaMo</t>
@@ -2699,7 +2710,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2720,6 +2731,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3206,31 +3223,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3239,121 +3253,125 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3361,20 +3379,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3760,7 +3778,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C323"/>
+  <dimension ref="A1:C324"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="74.875" customWidth="1"/>
@@ -3983,7 +4001,7 @@
       <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4013,10 +4031,10 @@
       <c r="A23" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4416,14 +4434,14 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
+    <row r="60" s="2" customFormat="1" ht="28.5" spans="1:3">
+      <c r="A60" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="5" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4465,18 +4483,18 @@
         <v>182</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
         <v>186</v>
@@ -4644,29 +4662,29 @@
         <v>230</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B81" t="s">
+        <v>233</v>
+      </c>
+      <c r="C81" t="s">
         <v>232</v>
-      </c>
-      <c r="C81" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
+        <v>235</v>
+      </c>
+      <c r="C82" t="s">
         <v>234</v>
-      </c>
-      <c r="C82" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4680,25 +4698,25 @@
         <v>238</v>
       </c>
     </row>
-    <row r="84" ht="28.5" spans="1:3">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>239</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" t="s">
         <v>240</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" ht="28.5" spans="1:3">
       <c r="A85" t="s">
         <v>242</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="4" t="s">
         <v>244</v>
       </c>
     </row>
@@ -4728,10 +4746,10 @@
       <c r="A88" t="s">
         <v>251</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" t="s">
         <v>252</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4739,10 +4757,10 @@
       <c r="A89" t="s">
         <v>254</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="7" t="s">
         <v>256</v>
       </c>
     </row>
@@ -4753,7 +4771,7 @@
       <c r="B90" t="s">
         <v>258</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4764,7 +4782,7 @@
       <c r="B91" t="s">
         <v>261</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="7" t="s">
         <v>262</v>
       </c>
     </row>
@@ -4944,25 +4962,25 @@
         <v>310</v>
       </c>
     </row>
-    <row r="108" ht="28.5" spans="1:3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>311</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" t="s">
         <v>312</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" ht="28.5" spans="1:3">
       <c r="A109" t="s">
         <v>314</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="4" t="s">
         <v>316</v>
       </c>
     </row>
@@ -5017,7 +5035,7 @@
       <c r="B114" t="s">
         <v>330</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5028,7 +5046,7 @@
       <c r="B115" t="s">
         <v>333</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="8" t="s">
         <v>334</v>
       </c>
     </row>
@@ -5039,7 +5057,7 @@
       <c r="B116" t="s">
         <v>336</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" t="s">
         <v>337</v>
       </c>
     </row>
@@ -5050,7 +5068,7 @@
       <c r="B117" t="s">
         <v>339</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="8" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5061,7 +5079,7 @@
       <c r="B118" t="s">
         <v>342</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" t="s">
         <v>343</v>
       </c>
     </row>
@@ -5072,7 +5090,7 @@
       <c r="B119" t="s">
         <v>345</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="7" t="s">
         <v>346</v>
       </c>
     </row>
@@ -5083,7 +5101,7 @@
       <c r="B120" t="s">
         <v>348</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" t="s">
         <v>349</v>
       </c>
     </row>
@@ -5094,7 +5112,7 @@
       <c r="B121" t="s">
         <v>351</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="7" t="s">
         <v>352</v>
       </c>
     </row>
@@ -5105,7 +5123,7 @@
       <c r="B122" t="s">
         <v>354</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5116,7 +5134,7 @@
       <c r="B123" t="s">
         <v>357</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="7" t="s">
         <v>358</v>
       </c>
     </row>
@@ -5127,7 +5145,7 @@
       <c r="B124" t="s">
         <v>360</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5138,7 +5156,7 @@
       <c r="B125" t="s">
         <v>363</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="7" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5149,7 +5167,7 @@
       <c r="B126" t="s">
         <v>366</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" t="s">
         <v>367</v>
       </c>
     </row>
@@ -5160,7 +5178,7 @@
       <c r="B127" t="s">
         <v>369</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="7" t="s">
         <v>370</v>
       </c>
     </row>
@@ -5171,7 +5189,7 @@
       <c r="B128" t="s">
         <v>372</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" t="s">
         <v>373</v>
       </c>
     </row>
@@ -5182,7 +5200,7 @@
       <c r="B129" t="s">
         <v>375</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="8" t="s">
         <v>376</v>
       </c>
     </row>
@@ -5193,7 +5211,7 @@
       <c r="B130" t="s">
         <v>378</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" t="s">
         <v>379</v>
       </c>
     </row>
@@ -5204,7 +5222,7 @@
       <c r="B131" t="s">
         <v>381</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="8" t="s">
         <v>382</v>
       </c>
     </row>
@@ -5215,7 +5233,7 @@
       <c r="B132" t="s">
         <v>384</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C132" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5226,7 +5244,7 @@
       <c r="B133" t="s">
         <v>387</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="8" t="s">
         <v>388</v>
       </c>
     </row>
@@ -5237,7 +5255,7 @@
       <c r="B134" t="s">
         <v>390</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C134" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5248,7 +5266,7 @@
       <c r="B135" t="s">
         <v>393</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="8" t="s">
         <v>394</v>
       </c>
     </row>
@@ -5259,7 +5277,7 @@
       <c r="B136" t="s">
         <v>396</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C136" t="s">
         <v>397</v>
       </c>
     </row>
@@ -5270,7 +5288,7 @@
       <c r="B137" t="s">
         <v>399</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="8" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5281,7 +5299,7 @@
       <c r="B138" t="s">
         <v>402</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="C138" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5292,7 +5310,7 @@
       <c r="B139" t="s">
         <v>405</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="8" t="s">
         <v>406</v>
       </c>
     </row>
@@ -5303,7 +5321,7 @@
       <c r="B140" t="s">
         <v>408</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" t="s">
         <v>409</v>
       </c>
     </row>
@@ -5314,7 +5332,7 @@
       <c r="B141" t="s">
         <v>411</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="8" t="s">
         <v>412</v>
       </c>
     </row>
@@ -5413,7 +5431,7 @@
       <c r="B150" t="s">
         <v>438</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="C150" t="s">
         <v>439</v>
       </c>
     </row>
@@ -5424,7 +5442,7 @@
       <c r="B151" t="s">
         <v>441</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="8" t="s">
         <v>442</v>
       </c>
     </row>
@@ -5435,7 +5453,7 @@
       <c r="B152" t="s">
         <v>444</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C152" t="s">
         <v>445</v>
       </c>
     </row>
@@ -5446,7 +5464,7 @@
       <c r="B153" t="s">
         <v>447</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="8" t="s">
         <v>448</v>
       </c>
     </row>
@@ -5678,18 +5696,18 @@
         <v>510</v>
       </c>
       <c r="C174" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B175" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C175" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -6170,15 +6188,15 @@
         <v>643</v>
       </c>
       <c r="B219" t="s">
-        <v>486</v>
+        <v>644</v>
       </c>
       <c r="C219" t="s">
-        <v>487</v>
+        <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B220" t="s">
         <v>489</v>
@@ -6189,95 +6207,95 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B221" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="C221" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B222" t="s">
-        <v>291</v>
+        <v>510</v>
       </c>
       <c r="C222" t="s">
-        <v>647</v>
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B223" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C223" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B224" t="s">
         <v>318</v>
       </c>
       <c r="C224" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B225" t="s">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="C225" t="s">
-        <v>271</v>
+        <v>654</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B226" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C226" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B227" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C227" t="s">
-        <v>655</v>
+        <v>280</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B228" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C228" t="s">
-        <v>280</v>
+        <v>658</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B229" t="s">
         <v>282</v>
@@ -6288,65 +6306,65 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B230" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C230" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B231" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C231" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B232" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C232" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B233" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C233" t="s">
-        <v>662</v>
+        <v>289</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B234" t="s">
         <v>300</v>
       </c>
       <c r="C234" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B235" t="s">
-        <v>666</v>
+        <v>303</v>
       </c>
       <c r="C235" t="s">
         <v>667</v>
@@ -6566,15 +6584,15 @@
         <v>725</v>
       </c>
       <c r="B255" t="s">
-        <v>551</v>
+        <v>726</v>
       </c>
       <c r="C255" t="s">
-        <v>552</v>
+        <v>727</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B256" t="s">
         <v>554</v>
@@ -6585,73 +6603,73 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B257" t="s">
         <v>557</v>
       </c>
       <c r="C257" t="s">
-        <v>728</v>
+        <v>558</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B258" t="s">
-        <v>291</v>
+        <v>560</v>
       </c>
       <c r="C258" t="s">
-        <v>647</v>
+        <v>731</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B259" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C259" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B260" t="s">
         <v>318</v>
       </c>
       <c r="C260" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B261" t="s">
-        <v>560</v>
+        <v>321</v>
       </c>
       <c r="C261" t="s">
-        <v>733</v>
+        <v>654</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B262" t="s">
         <v>563</v>
       </c>
       <c r="C262" t="s">
-        <v>564</v>
+        <v>736</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B263" t="s">
         <v>566</v>
@@ -6662,7 +6680,7 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B264" t="s">
         <v>569</v>
@@ -6673,29 +6691,29 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B265" t="s">
         <v>572</v>
       </c>
       <c r="C265" t="s">
-        <v>738</v>
+        <v>573</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B266" t="s">
         <v>575</v>
       </c>
       <c r="C266" t="s">
-        <v>576</v>
+        <v>741</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B267" t="s">
         <v>578</v>
@@ -6706,7 +6724,7 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B268" t="s">
         <v>581</v>
@@ -6717,7 +6735,7 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B269" t="s">
         <v>584</v>
@@ -6728,7 +6746,7 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B270" t="s">
         <v>587</v>
@@ -6739,40 +6757,40 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B271" t="s">
         <v>590</v>
       </c>
       <c r="C271" t="s">
-        <v>745</v>
+        <v>591</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B272" t="s">
         <v>593</v>
       </c>
       <c r="C272" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B273" t="s">
         <v>596</v>
       </c>
       <c r="C273" t="s">
-        <v>597</v>
+        <v>750</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B274" t="s">
         <v>599</v>
@@ -6783,7 +6801,7 @@
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B275" t="s">
         <v>602</v>
@@ -6794,51 +6812,51 @@
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B276" t="s">
-        <v>270</v>
+        <v>605</v>
       </c>
       <c r="C276" t="s">
-        <v>271</v>
+        <v>606</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C277" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B278" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C278" t="s">
-        <v>655</v>
+        <v>280</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C279" t="s">
-        <v>280</v>
+        <v>658</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B280" t="s">
         <v>282</v>
@@ -6849,95 +6867,95 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B281" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C281" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B282" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C282" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B283" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C283" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B284" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C284" t="s">
-        <v>662</v>
+        <v>289</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B285" t="s">
-        <v>605</v>
+        <v>300</v>
       </c>
       <c r="C285" t="s">
-        <v>606</v>
+        <v>665</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B286" t="s">
-        <v>300</v>
+        <v>608</v>
       </c>
       <c r="C286" t="s">
-        <v>664</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B287" t="s">
-        <v>608</v>
+        <v>303</v>
       </c>
       <c r="C287" t="s">
-        <v>763</v>
+        <v>667</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B288" t="s">
         <v>611</v>
       </c>
       <c r="C288" t="s">
-        <v>612</v>
+        <v>766</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B289" t="s">
         <v>614</v>
@@ -6948,7 +6966,7 @@
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B290" t="s">
         <v>617</v>
@@ -6959,7 +6977,7 @@
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B291" t="s">
         <v>620</v>
@@ -6970,7 +6988,7 @@
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B292" t="s">
         <v>623</v>
@@ -6981,7 +6999,7 @@
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B293" t="s">
         <v>626</v>
@@ -6992,7 +7010,7 @@
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B294" t="s">
         <v>629</v>
@@ -7003,7 +7021,7 @@
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B295" t="s">
         <v>632</v>
@@ -7014,7 +7032,7 @@
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B296" t="s">
         <v>635</v>
@@ -7025,35 +7043,35 @@
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B297" t="s">
         <v>638</v>
       </c>
       <c r="C297" t="s">
-        <v>774</v>
+        <v>639</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B298" t="s">
         <v>641</v>
       </c>
       <c r="C298" t="s">
-        <v>642</v>
+        <v>777</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B299" t="s">
-        <v>777</v>
+        <v>644</v>
       </c>
       <c r="C299" t="s">
-        <v>778</v>
+        <v>645</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -7167,164 +7185,175 @@
       </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="A310" s="8" t="s">
+      <c r="A310" t="s">
         <v>809</v>
       </c>
-      <c r="B310" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="C310" s="7" t="s">
-        <v>454</v>
+      <c r="B310" t="s">
+        <v>810</v>
+      </c>
+      <c r="C310" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="B311" s="9" t="s">
+      <c r="A311" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="B311" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="C311" s="7" t="s">
+      <c r="C311" s="8" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>812</v>
-      </c>
-      <c r="C312" s="7" t="s">
+      <c r="A312" s="9" t="s">
         <v>813</v>
       </c>
+      <c r="B312" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C312" s="8" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="A313" s="8" t="s">
+      <c r="A313" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="B313" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="C313" s="7" t="s">
-        <v>460</v>
+      <c r="B313" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="8" t="s">
-        <v>815</v>
-      </c>
-      <c r="B314" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="C314" s="7" t="s">
+      <c r="A314" s="9" t="s">
         <v>817</v>
       </c>
+      <c r="B314" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="8" t="s">
+      <c r="A315" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="B315" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="C315" s="7" t="s">
-        <v>466</v>
+      <c r="B315" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="8" t="s">
-        <v>819</v>
-      </c>
-      <c r="B316" s="9" t="s">
-        <v>820</v>
-      </c>
-      <c r="C316" s="7" t="s">
+      <c r="A316" s="9" t="s">
         <v>821</v>
       </c>
+      <c r="B316" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C316" s="8" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="8" t="s">
+      <c r="A317" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="B317" s="9" t="s">
+      <c r="B317" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="C317" s="7" t="s">
+      <c r="C317" s="8" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="8" t="s">
+      <c r="A318" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="B318" s="9" t="s">
+      <c r="B318" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C318" s="7" t="s">
+      <c r="C318" s="8" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="8" t="s">
+      <c r="A319" s="9" t="s">
         <v>828</v>
       </c>
-      <c r="B319" s="9" t="s">
+      <c r="B319" s="10" t="s">
         <v>829</v>
       </c>
-      <c r="C319" s="7" t="s">
+      <c r="C319" s="8" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="8" t="s">
+      <c r="A320" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C320" s="7" t="s">
+      <c r="C320" s="8" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="321" s="2" customFormat="1" spans="1:3">
-      <c r="A321" s="8" t="s">
+    <row r="321" spans="1:3">
+      <c r="A321" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="B321" s="10" t="s">
+      <c r="B321" t="s">
         <v>835</v>
       </c>
-      <c r="C321" s="7" t="s">
+      <c r="C321" s="8" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
-      <c r="A322" s="8" t="s">
+    <row r="322" s="3" customFormat="1" spans="1:3">
+      <c r="A322" s="9" t="s">
         <v>837</v>
       </c>
-      <c r="B322" s="9" t="s">
+      <c r="B322" s="11" t="s">
         <v>838</v>
       </c>
-      <c r="C322" s="9" t="s">
+      <c r="C322" s="8" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="8" t="s">
+      <c r="A323" s="9" t="s">
         <v>840</v>
       </c>
-      <c r="B323" t="s">
+      <c r="B323" s="10" t="s">
         <v>841</v>
       </c>
-      <c r="C323" t="s">
+      <c r="C323" s="10" t="s">
         <v>842</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="B324" t="s">
+        <v>844</v>
+      </c>
+      <c r="C324" t="s">
+        <v>845</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A85:C87 A9:C19 A20:B20 A21:C22 A231:C309 A229:B230 A228:C228 A227:B227 A24:C83 A206:B206 A207:C226 A23 A1:C7 A91:C107 A89:C89 B115:C115 A117:C117 A109:C112 B113:C113 A119:C119 A121:C121 A123:C123 A125:C125 A127:C127 A129:C129 A131:C131 A135:C135 A133:C133 A137:C137 A139:C139 A141:C149 A151:C151 A153:C205" numberStoredAsText="1"/>
+    <ignoredError sqref="A61:C84 A154:C206 A152:C152 A142:C150 A140:C140 A138:C138 A134:C134 A136:C136 A132:C132 A130:C130 A128:C128 A126:C126 A124:C124 A122:C122 A120:C120 B114:C114 A110:C113 A118:C118 B116:C116 A90:C90 A92:C108 A1:C7 A23 A208:C227 A207:B207 A24:C59 A228:B228 A229:C229 A230:B231 A232:C310 A21:C22 A20:B20 A9:C19 A86:C88" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/en-US.xlsx
+++ b/assets/翻译/en-US.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="en-US" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="848">
   <si>
     <t>key</t>
   </si>
@@ -2698,6 +2698,12 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>Ping</t>
+  </si>
+  <si>
+    <t>乒</t>
   </si>
 </sst>
 </file>
@@ -3778,7 +3784,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C324"/>
+  <dimension ref="A1:C325"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="74.875" customWidth="1"/>
@@ -7349,11 +7355,22 @@
         <v>845</v>
       </c>
     </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>846</v>
+      </c>
+      <c r="B325" t="s">
+        <v>847</v>
+      </c>
+      <c r="C325" t="s">
+        <v>846</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A61:C84 A154:C206 A152:C152 A142:C150 A140:C140 A138:C138 A134:C134 A136:C136 A132:C132 A130:C130 A128:C128 A126:C126 A124:C124 A122:C122 A120:C120 B114:C114 A110:C113 A118:C118 B116:C116 A90:C90 A92:C108 A1:C7 A23 A208:C227 A207:B207 A24:C59 A228:B228 A229:C229 A230:B231 A232:C310 A21:C22 A20:B20 A9:C19 A86:C88" numberStoredAsText="1"/>
+    <ignoredError sqref="A86:C88 A9:C19 A20:B20 A21:C22 A232:C310 A230:B231 A229:C229 A228:B228 A24:C59 A207:B207 A208:C227 A23 A1:C7 A92:C108 A90:C90 B116:C116 A118:C118 A110:C113 B114:C114 A120:C120 A122:C122 A124:C124 A126:C126 A128:C128 A130:C130 A132:C132 A136:C136 A134:C134 A138:C138 A140:C140 A142:C150 A152:C152 A154:C206 A61:C84" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/翻译/en-US.xlsx
+++ b/assets/翻译/en-US.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="en-US" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
     <t>Connecting</t>
   </si>
   <si>
-    <t>正在连接'</t>
+    <t>正在连接……</t>
   </si>
   <si>
     <t>Connecting...</t>
@@ -7370,7 +7370,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A86:C88 A9:C19 A20:B20 A21:C22 A232:C310 A230:B231 A229:C229 A228:B228 A24:C59 A207:B207 A208:C227 A23 A1:C7 A92:C108 A90:C90 B116:C116 A118:C118 A110:C113 B114:C114 A120:C120 A122:C122 A124:C124 A126:C126 A128:C128 A130:C130 A132:C132 A136:C136 A134:C134 A138:C138 A140:C140 A142:C150 A152:C152 A154:C206 A61:C84" numberStoredAsText="1"/>
+    <ignoredError sqref="A61:C84 A154:C206 A152:C152 A142:C150 A140:C140 A138:C138 A134:C134 A136:C136 A132:C132 A130:C130 A128:C128 A126:C126 A124:C124 A122:C122 A120:C120 B114:C114 A110:C113 A118:C118 B116:C116 A90:C90 A92:C108 A1:C7 A23 A208:C227 A207:B207 A24:C59 A228:B228 A229:C229 A230:B231 A232:C310 A21:C22 A20:B20 A9:C17 A18 C18 A19:C19 A86:C88" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>